--- a/eval/deepseek_proxyllm.xlsx
+++ b/eval/deepseek_proxyllm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>log</t>
         </is>
       </c>
@@ -453,20 +458,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>供应商A 都供哪些项目？</t>
+          <t>查询过去6个月内5B3A058-02零件的报价价格变化趋势，并用折线图展示结果</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SELECT DISTINCT bmw_project FROM Basic_Information WHERE vendor_supplier = '供应商A' LIMIT 50;</t>
+          <t>SELECT quotation_date, quotation_price_2 FROM Cost_Analysis WHERE bmw_part_number = '5B3A058-02' AND quotation_date &gt;= date('now', '-6 months') ORDER BY quotation_date LIMIT 50;</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[{'bmw_project': 'Project X'}]</t>
+          <t>[{'quotation_date': '2024-05-16', 'quotation_price_2': 2200}, {'quotation_date': '2024-07-21', 'quotation_price_2': 1927.5}, {'quotation_date': '2024-09-21', 'quotation_price_2': 2127.5}]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
@@ -475,20 +485,1699 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>零件5B3A058-01的报价总价是多少？</t>
+          <t>查询过去6个月内5B3A058-02零件的报价价格变化趋势，并用柱状图展示结果</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SELECT total_costs_9_0_X FROM Cost_Analysis WHERE bmw_part_number = '5B3A058-01' LIMIT 1;</t>
+          <t>SELECT quotation_date, quotation_price_2 FROM Cost_Analysis WHERE bmw_part_number = '5B3A058-02' AND quotation_date &gt;= date('now', '-6 months') ORDER BY quotation_date LIMIT 50;</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[{'total_costs_9_0_X': 1750}]</t>
+          <t>[{'quotation_date': '2024-05-16', 'quotation_price_2': 2200}, {'quotation_date': '2024-07-21', 'quotation_price_2': 1927.5}, {'quotation_date': '2024-09-21', 'quotation_price_2': 2127.5}]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>零件的变更索引与其开发成本之间是否存在某种模式，用折线图展示及结果</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SELECT bi.change_index_ai, ca.development_costs FROM Basic_Information bi JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[{'change_index_ai': 'Rev A', 'development_costs': 200}, {'change_index_ai': 'Rev B', 'development_costs': 230}, {'change_index_ai': 'Rev B', 'development_costs': 230}, {'change_index_ai': 'Rev B', 'development_costs': 250}, {'change_index_ai': 'Rev C', 'development_costs': 160}, {'change_index_ai': 'Rev C', 'development_costs': 180}, {'change_index_ai': 'Rev D', 'development_costs': 230}, {'change_index_ai': 'Rev D', 'development_costs': 230}, {'change_index_ai': 'Rev D', 'development_costs': 250}, {'change_index_ai': 'Rev E', 'development_costs': 160}, {'change_index_ai': 'Rev E', 'development_costs': 180}, {'change_index_ai': 'Rev F', 'development_costs': 220}, {'change_index_ai': 'Rev G', 'development_costs': 210}, {'change_index_ai': 'Rev G', 'development_costs': 260}, {'change_index_ai': 'Rev H', 'development_costs': 210}, {'change_index_ai': 'Rev H', 'development_costs': 260}, {'change_index_ai': 'Rev I', 'development_costs': 280}, {'change_index_ai': 'Rev J', 'development_costs': 180}]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>零件的变更索引与其开发成本之间是否存在某种模式，并用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SELECT bi.change_index_ai, SUM(ca.development_costs) AS total_development_costs FROM Basic_Information bi JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number GROUP BY bi.change_index_ai LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[{'change_index_ai': 'Rev A', 'total_development_costs': 200}, {'change_index_ai': 'Rev B', 'total_development_costs': 710}, {'change_index_ai': 'Rev C', 'total_development_costs': 340}, {'change_index_ai': 'Rev D', 'total_development_costs': 710}, {'change_index_ai': 'Rev E', 'total_development_costs': 340}, {'change_index_ai': 'Rev F', 'total_development_costs': 220}, {'change_index_ai': 'Rev G', 'total_development_costs': 470}, {'change_index_ai': 'Rev H', 'total_development_costs': 470}, {'change_index_ai': 'Rev I', 'total_development_costs': 280}, {'change_index_ai': 'Rev J', 'total_development_costs': 180}]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>请用柱状图来展示不同项目的零件数量、平均成本和总价值</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SELECT bi.bmw_project, COUNT(pa.bmw_part_number) AS part_count, AVG(ca.total_costs_9_0_X) AS avg_cost, SUM(ca.total_costs_9_0_X) AS total_value FROM Basic_Information bi JOIN Part_Assumption pa ON bi.bmw_part_number = pa.bmw_part_number JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number GROUP BY bi.bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'part_count': 6, 'avg_cost': 2041.6666666666667, 'total_value': 12250.0}, {'bmw_project': 'Project X', 'part_count': 7, 'avg_cost': 1689.2857142857142, 'total_value': 11825}, {'bmw_project': 'Project Y', 'part_count': 7, 'avg_cost': 2025.0, 'total_value': 14175.0}, {'bmw_project': 'Project Z', 'part_count': 12, 'avg_cost': 1875.0, 'total_value': 22500.0}]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>请用折线图来展示不同项目的零件数量、平均成本和总价值</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SELECT bi.bmw_project, COUNT(ca.bmw_part_number) AS part_count, AVG(ca.total_costs_9_0_X) AS avg_cost, SUM(ca.total_costs_9_0_X) AS total_value FROM Cost_Analysis ca JOIN Basic_Information bi ON ca.bmw_part_number = bi.bmw_part_number GROUP BY bi.bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'part_count': 3, 'avg_cost': 2041.6666666666667, 'total_value': 6125.0}, {'bmw_project': 'Project X', 'part_count': 5, 'avg_cost': 1760.0, 'total_value': 8800}, {'bmw_project': 'Project Y', 'part_count': 4, 'avg_cost': 2012.5, 'total_value': 8050.0}, {'bmw_project': 'Project Z', 'part_count': 6, 'avg_cost': 1875.0, 'total_value': 11250.0}]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>按供应商分类，列出所有零件的总生产成本，结果用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SELECT bi.vendor_supplier AS 供应商, SUM(ca.total_production_costs) AS 总生产成本 FROM Cost_Analysis ca JOIN Basic_Information bi ON ca.bmw_part_number = bi.bmw_part_number GROUP BY bi.vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[{'供应商': '供应商A', '总生产成本': 1500}, {'供应商': '供应商B', '总生产成本': 5250}, {'供应商': '供应商C', '总生产成本': 2600}, {'供应商': '供应商D', '总生产成本': 5250}, {'供应商': '供应商E', '总生产成本': 2600}, {'供应商': '供应商F', '总生产成本': 1650}, {'供应商': '供应商G', '总生产成本': 7050}, {'供应商': '供应商H', '总生产成本': 3450}]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>按供应商分类，列出所有零件的总生产成本，结果用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SELECT bi.vendor_supplier AS 供应商, SUM(ca.total_production_costs) AS 总生产成本 FROM Cost_Analysis ca JOIN Basic_Information bi ON ca.bmw_part_number = bi.bmw_part_number GROUP BY bi.vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[{'供应商': '供应商A', '总生产成本': 1500}, {'供应商': '供应商B', '总生产成本': 5250}, {'供应商': '供应商C', '总生产成本': 2600}, {'供应商': '供应商D', '总生产成本': 5250}, {'供应商': '供应商E', '总生产成本': 2600}, {'供应商': '供应商F', '总生产成本': 1650}, {'供应商': '供应商G', '总生产成本': 7050}, {'供应商': '供应商H', '总生产成本': 3450}]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>列出所有供应商拥有的零件种类数，用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SELECT vendor_supplier AS 供应商, COUNT(DISTINCT bmw_part_number) AS 零件种类数 FROM Basic_Information GROUP BY vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[{'供应商': '供应商A', '零件种类数': 1}, {'供应商': '供应商B', '零件种类数': 1}, {'供应商': '供应商C', '零件种类数': 1}, {'供应商': '供应商D', '零件种类数': 1}, {'供应商': '供应商E', '零件种类数': 1}, {'供应商': '供应商F', '零件种类数': 1}, {'供应商': '供应商G', '零件种类数': 1}, {'供应商': '供应商H', '零件种类数': 2}]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>列出所有供应商拥有的零件种类数，结果用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SELECT vendor_supplier, COUNT(DISTINCT bmw_part_number) AS part_count FROM Basic_Information GROUP BY vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[{'vendor_supplier': '供应商A', 'part_count': 1}, {'vendor_supplier': '供应商B', 'part_count': 1}, {'vendor_supplier': '供应商C', 'part_count': 1}, {'vendor_supplier': '供应商D', 'part_count': 1}, {'vendor_supplier': '供应商E', 'part_count': 1}, {'vendor_supplier': '供应商F', 'part_count': 1}, {'vendor_supplier': '供应商G', 'part_count': 1}, {'vendor_supplier': '供应商H', 'part_count': 2}]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>统计不同供应商的报价数量分布，饼状图展示</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SELECT vendor_supplier, COUNT(*) AS quotation_count FROM Basic_Information GROUP BY vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[{'vendor_supplier': '供应商A', 'quotation_count': 1}, {'vendor_supplier': '供应商B', 'quotation_count': 1}, {'vendor_supplier': '供应商C', 'quotation_count': 1}, {'vendor_supplier': '供应商D', 'quotation_count': 1}, {'vendor_supplier': '供应商E', 'quotation_count': 1}, {'vendor_supplier': '供应商F', 'quotation_count': 1}, {'vendor_supplier': '供应商G', 'quotation_count': 2}, {'vendor_supplier': '供应商H', 'quotation_count': 2}]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>统计不同供应商的报价数量分布，用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SELECT vendor_supplier, COUNT(*) AS quotation_count FROM Basic_Information GROUP BY vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[{'vendor_supplier': '供应商A', 'quotation_count': 1}, {'vendor_supplier': '供应商B', 'quotation_count': 1}, {'vendor_supplier': '供应商C', 'quotation_count': 1}, {'vendor_supplier': '供应商D', 'quotation_count': 1}, {'vendor_supplier': '供应商E', 'quotation_count': 1}, {'vendor_supplier': '供应商F', 'quotation_count': 1}, {'vendor_supplier': '供应商G', 'quotation_count': 2}, {'vendor_supplier': '供应商H', 'quotation_count': 2}]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>供应商A提供的不同项目所占的比例是多少，用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, COUNT(*) * 100.0 / (SELECT COUNT(*) FROM Basic_Information WHERE vendor_supplier = '供应商A') AS percentage FROM Basic_Information WHERE vendor_supplier = '供应商A' GROUP BY bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project X', 'percentage': 100.0}]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>供应商A提供的不同项目所占的比例是多少，用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, COUNT(*) * 100.0 / (SELECT COUNT(*) FROM Basic_Information WHERE vendor_supplier = '供应商A') AS percentage FROM Basic_Information WHERE vendor_supplier = '供应商A' GROUP BY bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project X', 'percentage': 100.0}]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>各供应商的总成本中，材料成本、制造成本和其他成本的分布如何。用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SELECT b.vendor_supplier AS 供应商, SUM(c.material_costs) AS 材料成本, SUM(c.manufacturing_costs) AS 制造成本, SUM(c.other_costs) AS 其他成本 FROM Cost_Analysis c JOIN Basic_Information b ON c.bmw_part_number = b.bmw_part_number GROUP BY b.vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[{'供应商': '供应商A', '材料成本': 1000, '制造成本': 500, '其他成本': 50}, {'供应商': '供应商B', '材料成本': 4200, '制造成本': 1750, '其他成本': 175.0}, {'供应商': '供应商C', '材料成本': 1750, '制造成本': 850, '其他成本': 85}, {'供应商': '供应商D', '材料成本': 4200, '制造成本': 1750, '其他成本': 175.0}, {'供应商': '供应商E', '材料成本': 1750, '制造成本': 850, '其他成本': 85}, {'供应商': '供应商F', '材料成本': 1100, '制造成本': 550, '其他成本': 55}, {'供应商': '供应商G', '材料成本': 4700, '制造成本': 2350, '其他成本': 235.0}, {'供应商': '供应商H', '材料成本': 2300, '制造成本': 1150, '其他成本': 115}]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>各供应商的总成本中，材料成本、制造成本和其他成本的分布如何。用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SELECT b.vendor_supplier AS 供应商, SUM(c.material_costs) AS 材料成本, SUM(c.manufacturing_costs) AS 制造成本, SUM(c.other_costs) AS 其他成本 FROM Cost_Analysis c JOIN Basic_Information b ON c.bmw_part_number = b.bmw_part_number GROUP BY b.vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[{'供应商': '供应商A', '材料成本': 1000, '制造成本': 500, '其他成本': 50}, {'供应商': '供应商B', '材料成本': 4200, '制造成本': 1750, '其他成本': 175.0}, {'供应商': '供应商C', '材料成本': 1750, '制造成本': 850, '其他成本': 85}, {'供应商': '供应商D', '材料成本': 4200, '制造成本': 1750, '其他成本': 175.0}, {'供应商': '供应商E', '材料成本': 1750, '制造成本': 850, '其他成本': 85}, {'供应商': '供应商F', '材料成本': 1100, '制造成本': 550, '其他成本': 55}, {'供应商': '供应商G', '材料成本': 4700, '制造成本': 2350, '其他成本': 235.0}, {'供应商': '供应商H', '材料成本': 2300, '制造成本': 1150, '其他成本': 115}]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>各供应商的总成本中，材料成本、制造成本和其他成本的分布如何。用折线图展示</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SELECT bmw_supplier_number, SUM(material_costs) AS total_material_costs, SUM(manufacturing_costs) AS total_manufacturing_costs, SUM(other_costs) AS total_other_costs FROM Cost_Analysis GROUP BY bmw_supplier_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SQLite 错误: no such column: bmw_supplier_number</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>不同零件在总报价中的占比是多少。结果用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SELECT b.bmw_part_number, b.parts_designation, c.quotation_price_2 AS total_quotation_price FROM Basic_Information b JOIN Cost_Analysis c ON b.bmw_part_number = c.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'parts_designation': 'Front Bumper', 'total_quotation_price': 1850}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Rear Light Assembly', 'total_quotation_price': 1927.5}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Rear Light Assembly', 'total_quotation_price': 2127.5}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Rear Light Assembly', 'total_quotation_price': 2200}, {'bmw_part_number': '5B3A058-03', 'parts_designation': 'Engine Mount', 'total_quotation_price': 1480}, {'bmw_part_number': '5B3A058-03', 'parts_designation': 'Engine Mount', 'total_quotation_price': 1720}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Transmission Assembly', 'total_quotation_price': 1927.5}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Transmission Assembly', 'total_quotation_price': 2127.5}, {'bmw_part_number': '5B3A058-02', 'parts_designation': 'Transmission Assembly', 'total_quotation_price': 2200}, {'bmw_part_number': '5B3A058-03', 'parts_designation': 'Brake Caliper', 'total_quotation_price': 1480}, {'bmw_part_number': '5B3A058-03', 'parts_designation': 'Brake Caliper', 'total_quotation_price': 1720}, {'bmw_part_number': '5B3A058-04', 'parts_designation': 'Steering Wheel', 'total_quotation_price': 2035}, {'bmw_part_number': '5B3A058-05', 'parts_designation': 'Suspension System', 'total_quotation_price': 1942.5}, {'bmw_part_number': '5B3A058-05', 'parts_designation': 'Suspension System', 'total_quotation_price': 2405}, {'bmw_part_number': '5B3A058-05', 'parts_designation': 'Exhaust System', 'total_quotation_price': 1942.5}, {'bmw_part_number': '5B3A058-05', 'parts_designation': 'Exhaust System', 'total_quotation_price': 2405}, {'bmw_part_number': '5B3A058-06', 'parts_designation': 'Fuel Pump', 'total_quotation_price': 2590}, {'bmw_part_number': '5B3A058-07', 'parts_designation': 'Battery Pack', 'total_quotation_price': 1665}]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>不同零件在总报价中的占比是多少。结果用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, (total_costs_9_0_X / SUM(total_costs_9_0_X) OVER ()) * 100 AS percentage_of_total FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'percentage_of_total': 8.348240906380441}, {'bmw_part_number': '5B3A058-02', 'percentage_of_total': 10.01788908765653}, {'bmw_part_number': '5B3A058-03', 'percentage_of_total': 7.751937984496124}, {'bmw_part_number': '5B3A058-04', 'percentage_of_total': 9.183064997018485}, {'bmw_part_number': '5B3A058-05', 'percentage_of_total': 10.852713178294573}, {'bmw_part_number': '5B3A058-05', 'percentage_of_total': 8.765652951699463}, {'bmw_part_number': '5B3A058-07', 'percentage_of_total': 7.5134168157423975}, {'bmw_part_number': '5B3A058-06', 'percentage_of_total': 11.68753726893262}, {'bmw_part_number': '5B3A058-03', 'percentage_of_total': 6.678592725104353}, {'bmw_part_number': '5B3A058-02', 'percentage_of_total': 9.600477042337507}, {'bmw_part_number': '5B3A058-02', 'percentage_of_total': 9.600477042337507}]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>各个供应商的制造地点分布比例如何。用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SELECT manufacturing_site_country_location, COUNT(*) AS count FROM Supplier_Assumption GROUP BY manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[{'manufacturing_site_country_location': 'China', 'count': 1}, {'manufacturing_site_country_location': 'Germany', 'count': 1}, {'manufacturing_site_country_location': 'Italy', 'count': 1}, {'manufacturing_site_country_location': 'Japan', 'count': 1}, {'manufacturing_site_country_location': 'Mexico', 'count': 1}, {'manufacturing_site_country_location': 'South Korea', 'count': 1}, {'manufacturing_site_country_location': 'UK', 'count': 1}, {'manufacturing_site_country_location': 'USA', 'count': 1}]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>各个供应商的制造地点分布比例如何。用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SELECT manufacturing_site_country_location, COUNT(*) AS supplier_count FROM Supplier_Assumption GROUP BY manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[{'manufacturing_site_country_location': 'China', 'supplier_count': 1}, {'manufacturing_site_country_location': 'Germany', 'supplier_count': 1}, {'manufacturing_site_country_location': 'Italy', 'supplier_count': 1}, {'manufacturing_site_country_location': 'Japan', 'supplier_count': 1}, {'manufacturing_site_country_location': 'Mexico', 'supplier_count': 1}, {'manufacturing_site_country_location': 'South Korea', 'supplier_count': 1}, {'manufacturing_site_country_location': 'UK', 'supplier_count': 1}, {'manufacturing_site_country_location': 'USA', 'supplier_count': 1}]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>各个BMW项目的零件报价占总报价的比例如何，用饼状图展示</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SELECT bi.bmw_project, SUM(ca.quotation_price_2) AS total_quotation_price, SUM(ca.quotation_price_2) / (SELECT SUM(quotation_price_2) FROM Cost_Analysis) AS proportion FROM Cost_Analysis ca JOIN Basic_Information bi ON ca.bmw_part_number = bi.bmw_part_number GROUP BY bi.bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'total_quotation_price': 6255.0, 'proportion': 0.28506323345106527}, {'bmw_project': 'Project X', 'total_quotation_price': 9305, 'proportion': 0.4240628916486271}, {'bmw_project': 'Project Y', 'total_quotation_price': 8290.0, 'proportion': 0.3778056283468155}, {'bmw_project': 'Project Z', 'total_quotation_price': 11895.0, 'proportion': 0.542098666970491}]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>各个BMW项目的零件报价占总报价的比例如何，用柱状图展示</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SELECT bi.bmw_project, SUM(ca.quotation_price_2) AS total_quotation, SUM(ca.quotation_price_2) / (SELECT SUM(quotation_price_2) FROM Cost_Analysis) AS quotation_percentage FROM Basic_Information bi JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number GROUP BY bi.bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'total_quotation': 6255.0, 'quotation_percentage': 0.28506323345106527}, {'bmw_project': 'Project X', 'total_quotation': 9305, 'quotation_percentage': 0.4240628916486271}, {'bmw_project': 'Project Y', 'total_quotation': 8290.0, 'quotation_percentage': 0.3778056283468155}, {'bmw_project': 'Project Z', 'total_quotation': 11895.0, 'quotation_percentage': 0.542098666970491}]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>零件重量和报价之间是否存在关联，用散点图展示。</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SELECT od.unpacked_parts_weight_kg, ca.quotation_price_2 FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[{'unpacked_parts_weight_kg': 5.5, 'quotation_price_2': 1850}, {'unpacked_parts_weight_kg': 3.2, 'quotation_price_2': 1927.5}, {'unpacked_parts_weight_kg': 3.2, 'quotation_price_2': 2127.5}, {'unpacked_parts_weight_kg': 3.2, 'quotation_price_2': 2200}, {'unpacked_parts_weight_kg': 2.8, 'quotation_price_2': 1480}, {'unpacked_parts_weight_kg': 2.8, 'quotation_price_2': 1720}, {'unpacked_parts_weight_kg': 7.5, 'quotation_price_2': 2035}, {'unpacked_parts_weight_kg': 4.2, 'quotation_price_2': 1942.5}, {'unpacked_parts_weight_kg': 4.2, 'quotation_price_2': 2405}, {'unpacked_parts_weight_kg': 3.8, 'quotation_price_2': 2590}, {'unpacked_parts_weight_kg': 1.9, 'quotation_price_2': 1665}]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>response_scatter_plot</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>零件重量和报价之间是否存在关联，用柱状图展示。</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SELECT AVG(od.unpacked_parts_weight_kg) AS avg_weight, AVG(ca.quotation_price_2) AS avg_price FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number GROUP BY od.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[{'avg_weight': 5.5, 'avg_price': 1850.0}, {'avg_weight': 3.2000000000000006, 'avg_price': 2085.0}, {'avg_weight': 2.8, 'avg_price': 1600.0}, {'avg_weight': 7.5, 'avg_price': 2035.0}, {'avg_weight': 4.2, 'avg_price': 2173.75}, {'avg_weight': 3.8, 'avg_price': 2590.0}, {'avg_weight': 1.9, 'avg_price': 1665.0}]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>生产批量大小与单件制造成本之间有什么关系，用散点图表示。</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SELECT pa.manufacturing_lot_size_parts, ca.manufacturing_costs FROM Part_Assumption pa JOIN Cost_Analysis ca ON pa.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[{'manufacturing_lot_size_parts': 1000, 'manufacturing_costs': 500}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 600}, {'manufacturing_lot_size_parts': 900, 'manufacturing_costs': 400}, {'manufacturing_lot_size_parts': 900, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1500, 'manufacturing_costs': 550}, {'manufacturing_lot_size_parts': 800, 'manufacturing_costs': 525}, {'manufacturing_lot_size_parts': 800, 'manufacturing_costs': 650}, {'manufacturing_lot_size_parts': 1300, 'manufacturing_costs': 525}, {'manufacturing_lot_size_parts': 1300, 'manufacturing_costs': 650}, {'manufacturing_lot_size_parts': 950, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1600, 'manufacturing_costs': 700}, {'manufacturing_lot_size_parts': 850, 'manufacturing_costs': 400}, {'manufacturing_lot_size_parts': 850, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 600}]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>response_scatter_plot</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>生产批量大小与单件制造成本之间有什么关系，用柱状图表示。</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SELECT pa.manufacturing_lot_size_parts, ca.manufacturing_costs FROM Part_Assumption pa JOIN Cost_Analysis ca ON pa.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[{'manufacturing_lot_size_parts': 1000, 'manufacturing_costs': 500}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1200, 'manufacturing_costs': 600}, {'manufacturing_lot_size_parts': 900, 'manufacturing_costs': 400}, {'manufacturing_lot_size_parts': 900, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1500, 'manufacturing_costs': 550}, {'manufacturing_lot_size_parts': 800, 'manufacturing_costs': 525}, {'manufacturing_lot_size_parts': 800, 'manufacturing_costs': 650}, {'manufacturing_lot_size_parts': 1300, 'manufacturing_costs': 525}, {'manufacturing_lot_size_parts': 1300, 'manufacturing_costs': 650}, {'manufacturing_lot_size_parts': 950, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1600, 'manufacturing_costs': 700}, {'manufacturing_lot_size_parts': 850, 'manufacturing_costs': 400}, {'manufacturing_lot_size_parts': 850, 'manufacturing_costs': 450}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 575}, {'manufacturing_lot_size_parts': 1400, 'manufacturing_costs': 600}]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>零件的尺寸（例如长度）与其运输成本之间是否存在相关性（散点图展示）</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SELECT od.part_dimensions_l_w_h_mm, ca.transport_costs_supplier_bmw FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[{'part_dimensions_l_w_h_mm': '1000x500x200', 'transport_costs_supplier_bmw': 30}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 34.5}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 34.5}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 35}, {'part_dimensions_l_w_h_mm': '600x300x100', 'transport_costs_supplier_bmw': 24}, {'part_dimensions_l_w_h_mm': '600x300x100', 'transport_costs_supplier_bmw': 28}, {'part_dimensions_l_w_h_mm': '1200x600x250', 'transport_costs_supplier_bmw': 33}, {'part_dimensions_l_w_h_mm': '900x450x180', 'transport_costs_supplier_bmw': 31.5}, {'part_dimensions_l_w_h_mm': '900x450x180', 'transport_costs_supplier_bmw': 39}, {'part_dimensions_l_w_h_mm': '700x350x140', 'transport_costs_supplier_bmw': 42}, {'part_dimensions_l_w_h_mm': '500x250x100', 'transport_costs_supplier_bmw': 27}]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>response_scatter_plot</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>零件的尺寸（例如长度）与其运输成本之间是否存在相关性（柱状图表示）</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SELECT od.part_dimensions_l_w_h_mm, ca.transport_costs_supplier_bmw FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[{'part_dimensions_l_w_h_mm': '1000x500x200', 'transport_costs_supplier_bmw': 30}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 34.5}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 34.5}, {'part_dimensions_l_w_h_mm': '800x400x150', 'transport_costs_supplier_bmw': 35}, {'part_dimensions_l_w_h_mm': '600x300x100', 'transport_costs_supplier_bmw': 24}, {'part_dimensions_l_w_h_mm': '600x300x100', 'transport_costs_supplier_bmw': 28}, {'part_dimensions_l_w_h_mm': '1200x600x250', 'transport_costs_supplier_bmw': 33}, {'part_dimensions_l_w_h_mm': '900x450x180', 'transport_costs_supplier_bmw': 31.5}, {'part_dimensions_l_w_h_mm': '900x450x180', 'transport_costs_supplier_bmw': 39}, {'part_dimensions_l_w_h_mm': '700x350x140', 'transport_costs_supplier_bmw': 42}, {'part_dimensions_l_w_h_mm': '500x250x100', 'transport_costs_supplier_bmw': 27}]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>供应商的年工作时间与其报价之间有什么关系（散点图展示）</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SELECT sa.hours_worked_per_year_h AS 年工作时间, ca.quotation_price_2 AS 报价  FROM Supplier_Assumption sa  JOIN Basic_Information bi ON sa.bmw_supplier_number = bi.bmw_supplier_number  JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number  LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[{'年工作时间': 2000, '报价': 1850}, {'年工作时间': 2200, '报价': 1927.5}, {'年工作时间': 2200, '报价': 2127.5}, {'年工作时间': 2200, '报价': 2200}, {'年工作时间': 1900, '报价': 1480}, {'年工作时间': 1900, '报价': 1720}, {'年工作时间': 2100, '报价': 1927.5}, {'年工作时间': 2100, '报价': 2127.5}, {'年工作时间': 2100, '报价': 2200}, {'年工作时间': 1950, '报价': 1480}, {'年工作时间': 1950, '报价': 1720}, {'年工作时间': 2050, '报价': 2035}, {'年工作时间': 2150, '报价': 1942.5}, {'年工作时间': 2150, '报价': 2405}, {'年工作时间': 2150, '报价': 1942.5}, {'年工作时间': 2150, '报价': 2405}, {'年工作时间': 2000, '报价': 2590}, {'年工作时间': 2000, '报价': 1665}]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>response_scatter_plot</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>供应商的年工作时间与其报价之间有什么关系（柱状图表示）</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SELECT sa.hours_worked_per_year_h AS 年工作时间, ca.quotation_price_2 AS 报价  FROM Supplier_Assumption sa  JOIN Basic_Information bi ON sa.bmw_supplier_number = bi.bmw_supplier_number  JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number  LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[{'年工作时间': 2000, '报价': 1850}, {'年工作时间': 2200, '报价': 1927.5}, {'年工作时间': 2200, '报价': 2127.5}, {'年工作时间': 2200, '报价': 2200}, {'年工作时间': 1900, '报价': 1480}, {'年工作时间': 1900, '报价': 1720}, {'年工作时间': 2100, '报价': 1927.5}, {'年工作时间': 2100, '报价': 2127.5}, {'年工作时间': 2100, '报价': 2200}, {'年工作时间': 1950, '报价': 1480}, {'年工作时间': 1950, '报价': 1720}, {'年工作时间': 2050, '报价': 2035}, {'年工作时间': 2150, '报价': 1942.5}, {'年工作时间': 2150, '报价': 2405}, {'年工作时间': 2150, '报价': 1942.5}, {'年工作时间': 2150, '报价': 2405}, {'年工作时间': 2000, '报价': 2590}, {'年工作时间': 2000, '报价': 1665}]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>请绘图展示零件重量、报价和年产量之间的关系（散点图展示）</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SELECT od.unpacked_parts_weight_kg AS 零件重量, ca.quotation_price_2 AS 报价, pa.peak_volume_year_parts_per_year AS 年产量 FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number JOIN Part_Assumption pa ON od.bmw_part_number = pa.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[{'零件重量': 5.5, '报价': 1850, '年产量': 25000}, {'零件重量': 3.2, '报价': 1927.5, '年产量': 30000}, {'零件重量': 3.2, '报价': 1927.5, '年产量': 33000}, {'零件重量': 3.2, '报价': 2127.5, '年产量': 30000}, {'零件重量': 3.2, '报价': 2127.5, '年产量': 33000}, {'零件重量': 3.2, '报价': 2200, '年产量': 30000}, {'零件重量': 3.2, '报价': 2200, '年产量': 33000}, {'零件重量': 2.8, '报价': 1480, '年产量': 21000}, {'零件重量': 2.8, '报价': 1480, '年产量': 22000}, {'零件重量': 2.8, '报价': 1720, '年产量': 21000}, {'零件重量': 2.8, '报价': 1720, '年产量': 22000}, {'零件重量': 7.5, '报价': 2035, '年产量': 35000}, {'零件重量': 4.2, '报价': 1942.5, '年产量': 20000}, {'零件重量': 4.2, '报价': 1942.5, '年产量': 32000}, {'零件重量': 4.2, '报价': 2405, '年产量': 20000}, {'零件重量': 4.2, '报价': 2405, '年产量': 32000}, {'零件重量': 3.8, '报价': 2590, '年产量': 37000}, {'零件重量': 1.9, '报价': 1665, '年产量': 23000}]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>response_scatter_plot</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>请绘图展示零件重量、报价和年产量之间的关系（柱状图表示）</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SELECT od.unpacked_parts_weight_kg AS 零件重量, ca.quotation_price_2 AS 报价, pa.peak_volume_year_parts_per_year AS 年产量 FROM Other_Data od JOIN Cost_Analysis ca ON od.bmw_part_number = ca.bmw_part_number JOIN Part_Assumption pa ON od.bmw_part_number = pa.bmw_part_number LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[{'零件重量': 5.5, '报价': 1850, '年产量': 25000}, {'零件重量': 3.2, '报价': 1927.5, '年产量': 30000}, {'零件重量': 3.2, '报价': 1927.5, '年产量': 33000}, {'零件重量': 3.2, '报价': 2127.5, '年产量': 30000}, {'零件重量': 3.2, '报价': 2127.5, '年产量': 33000}, {'零件重量': 3.2, '报价': 2200, '年产量': 30000}, {'零件重量': 3.2, '报价': 2200, '年产量': 33000}, {'零件重量': 2.8, '报价': 1480, '年产量': 21000}, {'零件重量': 2.8, '报价': 1480, '年产量': 22000}, {'零件重量': 2.8, '报价': 1720, '年产量': 21000}, {'零件重量': 2.8, '报价': 1720, '年产量': 22000}, {'零件重量': 7.5, '报价': 2035, '年产量': 35000}, {'零件重量': 4.2, '报价': 1942.5, '年产量': 20000}, {'零件重量': 4.2, '报价': 1942.5, '年产量': 32000}, {'零件重量': 4.2, '报价': 2405, '年产量': 20000}, {'零件重量': 4.2, '报价': 2405, '年产量': 32000}, {'零件重量': 3.8, '报价': 2590, '年产量': 37000}, {'零件重量': 1.9, '报价': 1665, '年产量': 23000}]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>比较不同国家的供应商数量、平均报价和总订单量（柱状图进行对比）</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SELECT sa.manufacturing_site_country_location AS country, COUNT(DISTINCT bi.bmw_supplier_number) AS supplier_count, AVG(ca.quotation_price_2) AS avg_quotation_price, SUM(ca.total_production_costs) AS total_order_amount FROM Supplier_Assumption sa JOIN Basic_Information bi ON sa.bmw_supplier_number = bi.bmw_supplier_number JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number GROUP BY sa.manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[{'country': 'China', 'supplier_count': 1, 'avg_quotation_price': 2085.0, 'total_order_amount': 5250}, {'country': 'Germany', 'supplier_count': 1, 'avg_quotation_price': 1850.0, 'total_order_amount': 1500}, {'country': 'Italy', 'supplier_count': 1, 'avg_quotation_price': 1600.0, 'total_order_amount': 2600}, {'country': 'Japan', 'supplier_count': 1, 'avg_quotation_price': 1600.0, 'total_order_amount': 2600}, {'country': 'Mexico', 'supplier_count': 1, 'avg_quotation_price': 2173.75, 'total_order_amount': 7050}, {'country': 'South Korea', 'supplier_count': 1, 'avg_quotation_price': 2127.5, 'total_order_amount': 3450}, {'country': 'UK', 'supplier_count': 1, 'avg_quotation_price': 2035.0, 'total_order_amount': 1650}, {'country': 'USA', 'supplier_count': 1, 'avg_quotation_price': 2085.0, 'total_order_amount': 5250}]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>比较不同国家的供应商数量、平均报价和总订单量（气泡图进行对比）</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SELECT sa.manufacturing_site_country_location AS country, COUNT(DISTINCT sa.bmw_supplier_number) AS supplier_count, AVG(ca.quotation_price_2) AS average_quotation, SUM(pa.total_volume_inquiry_parts) AS total_order_volume FROM Supplier_Assumption sa JOIN Basic_Information bi ON sa.bmw_supplier_number = bi.bmw_supplier_number JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number JOIN Part_Assumption pa ON ca.bmw_part_number = pa.bmw_part_number GROUP BY sa.manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[{'country': 'China', 'supplier_count': 1, 'average_quotation': 2085.0, 'total_order_volume': 780000}, {'country': 'Germany', 'supplier_count': 1, 'average_quotation': 1850.0, 'total_order_volume': 100000}, {'country': 'Italy', 'supplier_count': 1, 'average_quotation': 1600.0, 'total_order_volume': 350000}, {'country': 'Japan', 'supplier_count': 1, 'average_quotation': 1600.0, 'total_order_volume': 350000}, {'country': 'Mexico', 'supplier_count': 1, 'average_quotation': 2173.75, 'total_order_volume': 840000}, {'country': 'South Korea', 'supplier_count': 1, 'average_quotation': 2127.5, 'total_order_volume': 255000}, {'country': 'UK', 'supplier_count': 1, 'average_quotation': 2035.0, 'total_order_volume': 150000}, {'country': 'USA', 'supplier_count': 1, 'average_quotation': 2085.0, 'total_order_volume': 780000}]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>response_bubble_chart</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>比较不同国家的供应商数量、平均报价和总订单量（折线图进行对比）</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SELECT sa.manufacturing_site_country_location AS country, COUNT(DISTINCT sa.bmw_supplier_number) AS supplier_count, AVG(ca.quotation_price_2) AS average_quotation, SUM(ca.total_production_costs) AS total_order_amount FROM Supplier_Assumption sa JOIN Basic_Information bi ON sa.bmw_supplier_number = bi.bmw_supplier_number JOIN Cost_Analysis ca ON bi.bmw_part_number = ca.bmw_part_number GROUP BY sa.manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[{'country': 'China', 'supplier_count': 1, 'average_quotation': 2085.0, 'total_order_amount': 5250}, {'country': 'Germany', 'supplier_count': 1, 'average_quotation': 1850.0, 'total_order_amount': 1500}, {'country': 'Italy', 'supplier_count': 1, 'average_quotation': 1600.0, 'total_order_amount': 2600}, {'country': 'Japan', 'supplier_count': 1, 'average_quotation': 1600.0, 'total_order_amount': 2600}, {'country': 'Mexico', 'supplier_count': 1, 'average_quotation': 2173.75, 'total_order_amount': 7050}, {'country': 'South Korea', 'supplier_count': 1, 'average_quotation': 2127.5, 'total_order_amount': 3450}, {'country': 'UK', 'supplier_count': 1, 'average_quotation': 2035.0, 'total_order_amount': 1650}, {'country': 'USA', 'supplier_count': 1, 'average_quotation': 2085.0, 'total_order_amount': 5250}]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>用气泡图分析零件的材料成本、制造成本和报废率之间的关系</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SELECT material_costs, manufacturing_costs, scrap_costs FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[{'material_costs': 1000, 'manufacturing_costs': 500, 'scrap_costs': 50}, {'material_costs': 1200, 'manufacturing_costs': 600, 'scrap_costs': 60}, {'material_costs': 950, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'material_costs': 1100, 'manufacturing_costs': 550, 'scrap_costs': 55}, {'material_costs': 1300, 'manufacturing_costs': 650, 'scrap_costs': 65}, {'material_costs': 1050, 'manufacturing_costs': 525, 'scrap_costs': 52.5}, {'material_costs': 900, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'material_costs': 1400, 'manufacturing_costs': 700, 'scrap_costs': 70}, {'material_costs': 800, 'manufacturing_costs': 400, 'scrap_costs': 40}, {'material_costs': 1150, 'manufacturing_costs': 575, 'scrap_costs': 57.5}, {'material_costs': 1850, 'manufacturing_costs': 575, 'scrap_costs': 57.5}]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>response_bubble_chart</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>用柱状图分析零件的材料成本、制造成本和报废率之间的关系</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, material_costs, manufacturing_costs, scrap_costs FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'material_costs': 1000, 'manufacturing_costs': 500, 'scrap_costs': 50}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1200, 'manufacturing_costs': 600, 'scrap_costs': 60}, {'bmw_part_number': '5B3A058-03', 'material_costs': 950, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'bmw_part_number': '5B3A058-04', 'material_costs': 1100, 'manufacturing_costs': 550, 'scrap_costs': 55}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1300, 'manufacturing_costs': 650, 'scrap_costs': 65}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1050, 'manufacturing_costs': 525, 'scrap_costs': 52.5}, {'bmw_part_number': '5B3A058-07', 'material_costs': 900, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'bmw_part_number': '5B3A058-06', 'material_costs': 1400, 'manufacturing_costs': 700, 'scrap_costs': 70}, {'bmw_part_number': '5B3A058-03', 'material_costs': 800, 'manufacturing_costs': 400, 'scrap_costs': 40}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1150, 'manufacturing_costs': 575, 'scrap_costs': 57.5}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1850, 'manufacturing_costs': 575, 'scrap_costs': 57.5}]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>用折线图分析零件的材料成本、制造成本和报废率之间的关系</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, material_costs, manufacturing_costs, scrap_costs FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'material_costs': 1000, 'manufacturing_costs': 500, 'scrap_costs': 50}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1200, 'manufacturing_costs': 600, 'scrap_costs': 60}, {'bmw_part_number': '5B3A058-03', 'material_costs': 950, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'bmw_part_number': '5B3A058-04', 'material_costs': 1100, 'manufacturing_costs': 550, 'scrap_costs': 55}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1300, 'manufacturing_costs': 650, 'scrap_costs': 65}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1050, 'manufacturing_costs': 525, 'scrap_costs': 52.5}, {'bmw_part_number': '5B3A058-07', 'material_costs': 900, 'manufacturing_costs': 450, 'scrap_costs': 45}, {'bmw_part_number': '5B3A058-06', 'material_costs': 1400, 'manufacturing_costs': 700, 'scrap_costs': 70}, {'bmw_part_number': '5B3A058-03', 'material_costs': 800, 'manufacturing_costs': 400, 'scrap_costs': 40}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1150, 'manufacturing_costs': 575, 'scrap_costs': 57.5}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1850, 'manufacturing_costs': 575, 'scrap_costs': 57.5}]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>用饼状图展示各个BMW项目的零件数量分布</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, COUNT(*) AS part_count FROM Basic_Information GROUP BY bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'part_count': 1}, {'bmw_project': 'Project X', 'part_count': 4}, {'bmw_project': 'Project Y', 'part_count': 2}, {'bmw_project': 'Project Z', 'part_count': 3}]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>用柱状图展示各个BMW项目的零件数量分布</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, COUNT(bmw_part_number) AS part_count FROM Basic_Information GROUP BY bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'part_count': 1}, {'bmw_project': 'Project X', 'part_count': 4}, {'bmw_project': 'Project Y', 'part_count': 2}, {'bmw_project': 'Project Z', 'part_count': 3}]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>用折线图展示各个BMW项目的零件数量分布</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, COUNT(bmw_part_number) AS part_count FROM Basic_Information GROUP BY bmw_project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[{'bmw_project': 'Project W', 'part_count': 1}, {'bmw_project': 'Project X', 'part_count': 4}, {'bmw_project': 'Project Y', 'part_count': 2}, {'bmw_project': 'Project Z', 'part_count': 3}]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>用饼状图展示不同供应商的市场份额</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SELECT vendor_supplier, SUM(total_production_costs) AS total_cost FROM Cost_Analysis GROUP BY vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SQLite 错误: no such column: vendor_supplier</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>用柱状图展示不同供应商的市场份额</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SELECT b.vendor_supplier AS supplier, SUM(p.total_volume_inquiry_parts) AS market_share FROM Basic_Information b JOIN Part_Assumption p ON b.bmw_part_number = p.bmw_part_number GROUP BY b.vendor_supplier LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[{'supplier': '供应商A', 'market_share': 100000}, {'supplier': '供应商B', 'market_share': 260000}, {'supplier': '供应商C', 'market_share': 175000}, {'supplier': '供应商D', 'market_share': 260000}, {'supplier': '供应商E', 'market_share': 175000}, {'supplier': '供应商F', 'market_share': 150000}, {'supplier': '供应商G', 'market_share': 420000}, {'supplier': '供应商H', 'market_share': 255000}]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>用折线图示不同供应商的市场份额</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>提供的表结构信息不足以生成 sql 查询。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SQLite 错误: near "提供的表结构信息不足以生成": syntax error</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>用环形图来展示各个生产国家的成本构成</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SELECT sa.manufacturing_site_country_location AS country, SUM(ca.total_costs_9_0_X) AS total_costs FROM Supplier_Assumption sa JOIN Cost_Analysis ca ON sa.bmw_supplier_number = ca.bmw_part_number GROUP BY sa.manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>response_donut_chart</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>用饼状图来展示各个生产国家的成本构成</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SELECT sa.manufacturing_site_country_location AS production_country, SUM(ca.total_costs_9_0_X) AS total_cost FROM Cost_Analysis ca JOIN Supplier_Assumption sa ON ca.bmw_part_number = sa.bmw_supplier_number GROUP BY sa.manufacturing_site_country_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>用柱状图展示不同BMW零件编号的报价构成</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, quotation_price_2 FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'quotation_price_2': 1850}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 2200}, {'bmw_part_number': '5B3A058-03', 'quotation_price_2': 1720}, {'bmw_part_number': '5B3A058-04', 'quotation_price_2': 2035}, {'bmw_part_number': '5B3A058-05', 'quotation_price_2': 2405}, {'bmw_part_number': '5B3A058-05', 'quotation_price_2': 1942.5}, {'bmw_part_number': '5B3A058-07', 'quotation_price_2': 1665}, {'bmw_part_number': '5B3A058-06', 'quotation_price_2': 2590}, {'bmw_part_number': '5B3A058-03', 'quotation_price_2': 1480}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 2127.5}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 1927.5}]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>用饼状图展示不同BMW零件编号的报价构成</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, quotation_price_2 FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'quotation_price_2': 1850}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 2200}, {'bmw_part_number': '5B3A058-03', 'quotation_price_2': 1720}, {'bmw_part_number': '5B3A058-04', 'quotation_price_2': 2035}, {'bmw_part_number': '5B3A058-05', 'quotation_price_2': 2405}, {'bmw_part_number': '5B3A058-05', 'quotation_price_2': 1942.5}, {'bmw_part_number': '5B3A058-07', 'quotation_price_2': 1665}, {'bmw_part_number': '5B3A058-06', 'quotation_price_2': 2590}, {'bmw_part_number': '5B3A058-03', 'quotation_price_2': 1480}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 2127.5}, {'bmw_part_number': '5B3A058-02', 'quotation_price_2': 1927.5}]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>response_pie_chart</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>用折线图展示不同BMW零件编号的报价构成</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SELECT bmw_part_number, material_costs, manufacturing_costs, total_production_costs, total_costs_9_0_X, quotation_price_2 FROM Cost_Analysis LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[{'bmw_part_number': '5B3A058-01', 'material_costs': 1000, 'manufacturing_costs': 500, 'total_production_costs': 1500, 'total_costs_9_0_X': 1750, 'quotation_price_2': 1850}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1200, 'manufacturing_costs': 600, 'total_production_costs': 1800, 'total_costs_9_0_X': 2100, 'quotation_price_2': 2200}, {'bmw_part_number': '5B3A058-03', 'material_costs': 950, 'manufacturing_costs': 450, 'total_production_costs': 1400, 'total_costs_9_0_X': 1625, 'quotation_price_2': 1720}, {'bmw_part_number': '5B3A058-04', 'material_costs': 1100, 'manufacturing_costs': 550, 'total_production_costs': 1650, 'total_costs_9_0_X': 1925, 'quotation_price_2': 2035}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1300, 'manufacturing_costs': 650, 'total_production_costs': 1950, 'total_costs_9_0_X': 2275, 'quotation_price_2': 2405}, {'bmw_part_number': '5B3A058-05', 'material_costs': 1050, 'manufacturing_costs': 525, 'total_production_costs': 1575, 'total_costs_9_0_X': 1837.5, 'quotation_price_2': 1942.5}, {'bmw_part_number': '5B3A058-07', 'material_costs': 900, 'manufacturing_costs': 450, 'total_production_costs': 1350, 'total_costs_9_0_X': 1575, 'quotation_price_2': 1665}, {'bmw_part_number': '5B3A058-06', 'material_costs': 1400, 'manufacturing_costs': 700, 'total_production_costs': 2100, 'total_costs_9_0_X': 2450, 'quotation_price_2': 2590}, {'bmw_part_number': '5B3A058-03', 'material_costs': 800, 'manufacturing_costs': 400, 'total_production_costs': 1200, 'total_costs_9_0_X': 1400, 'quotation_price_2': 1480}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1150, 'manufacturing_costs': 575, 'total_production_costs': 1725, 'total_costs_9_0_X': 2012.5, 'quotation_price_2': 2127.5}, {'bmw_part_number': '5B3A058-02', 'material_costs': 1850, 'manufacturing_costs': 575, 'total_production_costs': 1725, 'total_costs_9_0_X': 2012.5, 'quotation_price_2': 1927.5}]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>用柱状图展示各个供应商的产能利用率分布</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>提供的表结构信息不足以生成 sql 查询。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SQLite 错误: near "提供的表结构信息不足以生成": syntax error</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>用饼状图展示各个供应商的产能利用率分布</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>提供的表结构信息不足以生成 sql 查询。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SQLite 错误: near "提供的表结构信息不足以生成": syntax error</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>面积图展示过去一年内每月的累积报价总额变化趋势</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SELECT strftime('%Y-%m', quotation_date) AS month, SUM(total_production_costs) OVER (ORDER BY strftime('%Y-%m', quotation_date)) AS cumulative_total_production_costs FROM Cost_Analysis WHERE quotation_date &gt;= date('now', '-1 year') ORDER BY month LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[{'month': '2024-05', 'cumulative_total_production_costs': 3375}, {'month': '2024-05', 'cumulative_total_production_costs': 3375}, {'month': '2024-07', 'cumulative_total_production_costs': 5100}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}]</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>response_area_chart</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>折线图展示过去一年内每月的累积报价总额变化趋势</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SELECT strftime('%Y-%m', quotation_date) AS month, SUM(total_production_costs) OVER (ORDER BY strftime('%Y-%m', quotation_date)) AS cumulative_total_production_costs FROM Cost_Analysis WHERE quotation_date &gt;= date('now', '-1 year') ORDER BY month LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[{'month': '2024-05', 'cumulative_total_production_costs': 3375}, {'month': '2024-05', 'cumulative_total_production_costs': 3375}, {'month': '2024-07', 'cumulative_total_production_costs': 5100}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}, {'month': '2024-09', 'cumulative_total_production_costs': 10275}]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>柱状图展示过去一年内每月的累积报价总额变化趋势</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SELECT strftime('%Y-%m', quotation_date) AS month, SUM(total_production_costs) AS cumulative_total_costs FROM Cost_Analysis WHERE quotation_date &gt;= date('now', '-1 year') GROUP BY month ORDER BY month;</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[{'month': '2024-05', 'cumulative_total_costs': 3375}, {'month': '2024-07', 'cumulative_total_costs': 1725}, {'month': '2024-09', 'cumulative_total_costs': 5175}]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>用折线图展示各个供应商在过去18个月内的市场份额变化</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>提供的表结构信息不足以生成 sql 查询。</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SQLite 错误: near "提供的表结构信息不足以生成": syntax error</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>用柱状图展示各个供应商在过去18个月内的市场份额变化</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SELECT b.vendor_supplier, strftime('%Y-%m', c.quotation_date) AS month_year, COUNT(c.id) AS order_count FROM Basic_Information b JOIN Cost_Analysis c ON b.bmw_part_number = c.bmw_part_number WHERE c.quotation_date &gt;= date('now', '-18 months') GROUP BY b.vendor_supplier, month_year ORDER BY month_year LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[{'vendor_supplier': '供应商B', 'month_year': '2024-05', 'order_count': 1}, {'vendor_supplier': '供应商D', 'month_year': '2024-05', 'order_count': 1}, {'vendor_supplier': '供应商G', 'month_year': '2024-05', 'order_count': 2}, {'vendor_supplier': '供应商B', 'month_year': '2024-07', 'order_count': 1}, {'vendor_supplier': '供应商D', 'month_year': '2024-07', 'order_count': 1}, {'vendor_supplier': '供应商A', 'month_year': '2024-09', 'order_count': 1}, {'vendor_supplier': '供应商B', 'month_year': '2024-09', 'order_count': 1}, {'vendor_supplier': '供应商D', 'month_year': '2024-09', 'order_count': 1}, {'vendor_supplier': '供应商G', 'month_year': '2024-09', 'order_count': 2}]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>用面积图来显示不同成本类型（如材料成本、制造成本等）在过去一年内的累积变化</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SELECT strftime('%Y-%m', quotation_date) AS month_year, SUM(material_costs) AS material_costs, SUM(manufacturing_costs) AS manufacturing_costs, SUM(total_production_costs) AS total_production_costs FROM Cost_Analysis WHERE quotation_date &gt;= date('now', '-1 year') GROUP BY month_year ORDER BY month_year;</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[{'month_year': '2024-05', 'material_costs': 2250, 'manufacturing_costs': 1125, 'total_production_costs': 3375}, {'month_year': '2024-07', 'material_costs': 1850, 'manufacturing_costs': 575, 'total_production_costs': 1725}, {'month_year': '2024-09', 'material_costs': 3450, 'manufacturing_costs': 1725, 'total_production_costs': 5175}]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>response_area_chart</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>用热力图来展示不同国家和不同BMW项目的零件数量分布</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SELECT manufacturing_site_country_location AS country, bmw_project AS project, COUNT(bmw_part_number) AS part_count FROM Basic_Information JOIN Supplier_Assumption ON Basic_Information.bmw_supplier_number = Supplier_Assumption.bmw_supplier_number GROUP BY country, project LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[{'country': 'China', 'project': 'Project Y', 'part_count': 1}, {'country': 'Germany', 'project': 'Project X', 'part_count': 1}, {'country': 'Italy', 'project': 'Project X', 'part_count': 1}, {'country': 'Japan', 'project': 'Project Z', 'part_count': 1}, {'country': 'Mexico', 'project': 'Project Z', 'part_count': 2}, {'country': 'South Korea', 'project': 'Project X', 'part_count': 2}, {'country': 'UK', 'project': 'Project Y', 'part_count': 1}, {'country': 'USA', 'project': 'Project W', 'part_count': 1}]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>response_heatmap</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>供应商在不同国家的制造地点和分销地点的分布情况如何？结果用柱状图表示</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SELECT manufacturing_site_country_location AS 制造地点, country_of_distribution_location AS 分销地点, COUNT(*) AS 数量 FROM Supplier_Assumption GROUP BY manufacturing_site_country_location, country_of_distribution_location LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[{'制造地点': 'China', '分销地点': 'USA', '数量': 1}, {'制造地点': 'Germany', '分销地点': 'France', '数量': 1}, {'制造地点': 'Italy', '分销地点': 'Spain', '数量': 1}, {'制造地点': 'Japan', '分销地点': 'South Korea', '数量': 1}, {'制造地点': 'Mexico', '分销地点': 'USA', '数量': 1}, {'制造地点': 'South Korea', '分销地点': 'Japan', '数量': 1}, {'制造地点': 'UK', '分销地点': 'Germany', '数量': 1}, {'制造地点': 'USA', '分销地点': 'Canada', '数量': 1}]</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>response_bar_chart</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>哪些项目的生产开始日期在2022年之后（柱状图）</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SELECT bmw_project, production_start_sop_mm_yyyy FROM Part_Assumption WHERE production_start_sop_mm_yyyy &gt; '2022-12-31' LIMIT 50;</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>SQLite 错误: no such column: bmw_project</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>与去年同期相比,2023年前三季度新获订单的平均报价变动幅度是多少（折线图表示）</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>WITH q3_2023 AS (SELECT AVG(quotation_price_2) AS avg_price_2023 FROM Cost_Analysis WHERE strftime('%Y', quotation_date) = '2023' AND strftime('%m', quotation_date) BETWEEN '01' AND '09'), q3_2022 AS (SELECT AVG(quotation_price_2) AS avg_price_2022 FROM Cost_Analysis WHERE strftime('%Y', quotation_date) = '2022' AND strftime('%m', quotation_date) BETWEEN '01' AND '09') SELECT (avg_price_2023 - avg_price_2022) / avg_price_2022 * 100 AS price_change_percentage FROM q3_2023, q3_2022;</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[{'price_change_percentage': -13.953488372093023}]</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>response_line_chart</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>零件5B3A058-01的一次性payment是多少？</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SELECT one_time_payments FROM Cost_Analysis WHERE bmw_part_number = '5B3A058-01' LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[{'one_time_payments': 500}]</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>零件5B3A058-01加工总价是多少？</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SELECT total_production_costs FROM Cost_Analysis WHERE bmw_part_number = '5B3A058-01' LIMIT 1;</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[{'total_production_costs': 1500}]</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>response_table</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>Success</t>
         </is>
